--- a/KurseMscECMX_SoSe26.xlsx
+++ b/KurseMscECMX_SoSe26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vineet.Dairashri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4839E33-E248-42DA-97D9-ACA8DB53E042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669E8CD6-9CD7-4AC1-B624-B23FBC26BCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="579">
   <si>
     <t>Kurs</t>
   </si>
@@ -207,9 +207,6 @@
     <t>Applied Economics I</t>
   </si>
   <si>
-    <t>Finance I</t>
-  </si>
-  <si>
     <t>Prof. Dr. Peter N. Posch</t>
   </si>
   <si>
@@ -310,9 +307,6 @@
   </si>
   <si>
     <t>Prof. Dr. Marie Paul</t>
-  </si>
-  <si>
-    <t>Quantitative Finance</t>
   </si>
   <si>
     <t xml:space="preserve">MHB </t>
@@ -1212,9 +1206,6 @@
     <t>As offered</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>https://www.lsf.tu-dortmund.de/qisserver/rds?state=verpublish&amp;status=init&amp;vmfile=no&amp;publishid=297223&amp;moduleCall=webInfo&amp;publishConfFile=webInfo&amp;publishSubDir=veranstaltung</t>
   </si>
   <si>
@@ -1778,6 +1769,24 @@
   </si>
   <si>
     <t>https://www.lsf.tu-dortmund.de/qisserver/rds?state=verpublish&amp;status=init&amp;vmfile=no&amp;publishid=316210&amp;moduleCall=webInfo&amp;publishConfFile=webInfo&amp;publishSubDir=veranstaltung</t>
+  </si>
+  <si>
+    <t>Applied Econometrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Finance I</t>
+  </si>
+  <si>
+    <t>Faculty of Business Administration and Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Faculty of Management and Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Industrial Organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Internationale Wirtschaft II (International Economics)</t>
   </si>
 </sst>
 </file>
@@ -2973,175 +2982,175 @@
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>145</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3149,295 +3158,295 @@
         <v>48</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="E39" s="91"/>
       <c r="G39" s="66"/>
     </row>
     <row r="40" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="55" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G40" s="66"/>
     </row>
     <row r="41" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="62" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3447,24 +3456,24 @@
     </row>
     <row r="45" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3472,21 +3481,21 @@
         <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3494,32 +3503,32 @@
         <v>18</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C50" s="30" t="s">
         <v>303</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3527,10 +3536,10 @@
         <v>25</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3538,21 +3547,21 @@
         <v>20</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C53" s="30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3560,10 +3569,10 @@
         <v>28</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3571,10 +3580,10 @@
         <v>31</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -3582,65 +3591,65 @@
         <v>45</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="30" t="s">
         <v>128</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="1" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
@@ -4057,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -4072,42 +4081,42 @@
         <v>5</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N1" s="103"/>
       <c r="S1" s="41"/>
     </row>
     <row r="2" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C2" s="5" t="str">
         <f>VLOOKUP($E2,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Mathematical Statistics with Applications in Biometrics</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>49</v>
@@ -4116,13 +4125,13 @@
         <v>10</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K2" s="35">
         <v>3</v>
@@ -4131,29 +4140,29 @@
         <v>11</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N2" s="104" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S2" s="41"/>
     </row>
     <row r="3" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C3" s="5" t="str">
         <f>VLOOKUP($E3,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Business and Social Statistics</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>49</v>
@@ -4162,13 +4171,13 @@
         <v>10</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J3" s="48" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K3" s="35">
         <v>4</v>
@@ -4177,29 +4186,29 @@
         <v>11</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N3" s="104" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S3" s="41"/>
     </row>
-    <row r="4" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="5" t="str">
         <f>VLOOKUP($E4,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Econometrics and Statistics</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>49</v>
@@ -4208,13 +4217,13 @@
         <v>39</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J4" s="93" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="K4" s="36">
         <v>5</v>
@@ -4223,10 +4232,10 @@
         <v>11</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N4" s="115" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O4" s="29"/>
       <c r="P4" s="29"/>
@@ -5237,17 +5246,17 @@
     </row>
     <row r="5" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="14" t="str">
         <f>VLOOKUP($E5,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Econometrics</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>15</v>
@@ -5262,10 +5271,10 @@
         <v>9</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J5" s="39" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K5" s="22">
         <v>5</v>
@@ -5274,10 +5283,10 @@
         <v>11</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N5" s="104" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O5" s="96"/>
       <c r="P5" s="12"/>
@@ -6286,12 +6295,12 @@
       <c r="AME5" s="12"/>
       <c r="AMF5" s="12"/>
     </row>
-    <row r="6" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1020" s="17" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="18" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C6" s="5" t="str">
         <f>VLOOKUP($E6,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -6301,7 +6310,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>49</v>
@@ -6310,13 +6319,13 @@
         <v>39</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="J6" s="93" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K6" s="36">
         <v>6</v>
@@ -6325,13 +6334,13 @@
         <v>11</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N6" s="115" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O6" s="95" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="P6" s="28"/>
       <c r="Q6" s="28"/>
@@ -7339,22 +7348,22 @@
       <c r="AME6" s="28"/>
       <c r="AMF6" s="28"/>
     </row>
-    <row r="7" spans="1:1020" s="29" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1020" s="29" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" s="13" t="str">
         <f>VLOOKUP($E7,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Econometrics</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>49</v>
@@ -7363,13 +7372,13 @@
         <v>16</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J7" s="93" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="K7" s="35">
         <v>7</v>
@@ -7378,10 +7387,10 @@
         <v>11</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N7" s="115" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -8392,10 +8401,10 @@
     </row>
     <row r="8" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="24" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C8" s="15" t="str">
         <f>VLOOKUP($E8,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -8405,22 +8414,22 @@
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J8" s="39" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K8" s="25">
         <v>18</v>
@@ -8429,10 +8438,10 @@
         <v>11</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N8" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
@@ -9441,12 +9450,12 @@
       <c r="AME8" s="12"/>
       <c r="AMF8" s="12"/>
     </row>
-    <row r="9" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="31" t="str">
         <f>VLOOKUP($E9,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -9456,22 +9465,22 @@
         <v>8</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J9" s="93" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="K9" s="25">
         <v>19</v>
@@ -9480,10 +9489,10 @@
         <v>11</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N9" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
@@ -10492,12 +10501,12 @@
       <c r="AME9" s="12"/>
       <c r="AMF9" s="12"/>
     </row>
-    <row r="10" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C10" s="31" t="str">
         <f>VLOOKUP($E10,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -10507,22 +10516,22 @@
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J10" s="93" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="K10" s="25">
         <v>20</v>
@@ -10531,10 +10540,10 @@
         <v>11</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N10" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
@@ -11545,35 +11554,35 @@
     </row>
     <row r="11" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C11" s="31" t="str">
         <f>VLOOKUP($E11,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Applied Microeconomics</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="K11" s="25">
         <v>21</v>
@@ -11582,10 +11591,10 @@
         <v>11</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N11" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
@@ -12594,37 +12603,37 @@
       <c r="AME11" s="12"/>
       <c r="AMF11" s="12"/>
     </row>
-    <row r="12" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C12" s="31" t="str">
         <f>VLOOKUP($E12,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Empirical Economics</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J12" s="93" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="K12" s="25">
         <v>22</v>
@@ -12633,10 +12642,10 @@
         <v>11</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N12" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
@@ -13647,35 +13656,35 @@
     </row>
     <row r="13" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C13" s="31" t="str">
         <f>VLOOKUP($E13,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Macroeconomics</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J13" s="39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K13" s="25">
         <v>23</v>
@@ -13684,10 +13693,10 @@
         <v>11</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N13" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
@@ -14698,10 +14707,10 @@
     </row>
     <row r="14" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C14" s="31" t="str">
         <f>VLOOKUP($E14,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -14711,22 +14720,22 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K14" s="25">
         <v>24</v>
@@ -14735,10 +14744,10 @@
         <v>11</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N14" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
@@ -15749,35 +15758,35 @@
     </row>
     <row r="15" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C15" s="31" t="str">
         <f>VLOOKUP($E15,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Applied Microeconomics</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J15" s="39" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K15" s="25">
         <v>25</v>
@@ -15786,44 +15795,44 @@
         <v>11</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N15" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S15" s="26"/>
     </row>
     <row r="16" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="24" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C16" s="31" t="str">
         <f>VLOOKUP($E16,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Applied Microeconomics</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J16" s="39" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K16" s="25">
         <v>26</v>
@@ -15832,44 +15841,44 @@
         <v>11</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N16" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S16" s="26"/>
     </row>
-    <row r="17" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="24" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C17" s="31" t="str">
         <f>VLOOKUP($E17,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Applied Microeconomics</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J17" s="93" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K17" s="25">
         <v>27</v>
@@ -15878,43 +15887,43 @@
         <v>11</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N17" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="31" t="str">
         <f>VLOOKUP($E18,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair for Public and Regional Economics</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J18" s="93" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="K18" s="25">
         <v>28</v>
@@ -15923,18 +15932,18 @@
         <v>11</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N18" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>VLOOKUP($E19,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -15944,22 +15953,22 @@
         <v>8</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J19" s="39" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K19" s="25">
         <v>29</v>
@@ -15968,43 +15977,43 @@
         <v>11</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N19" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C20" s="31" t="str">
         <f>VLOOKUP($E20,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistics/Econometrics</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K20" s="25">
         <v>31</v>
@@ -16013,43 +16022,43 @@
         <v>11</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N20" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="31" t="str">
         <f>VLOOKUP($E21,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistics/Econometrics</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J21" s="39" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K21" s="25">
         <v>32</v>
@@ -16058,18 +16067,18 @@
         <v>11</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N21" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C22" s="31" t="str">
         <f>VLOOKUP($E22,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16079,22 +16088,22 @@
         <v>14</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="K22" s="25">
         <v>33</v>
@@ -16103,19 +16112,19 @@
         <v>11</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N22" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O22" s="44"/>
     </row>
     <row r="23" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="24" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C23" s="15" t="str">
         <f>VLOOKUP($E23,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16125,22 +16134,22 @@
         <v>8</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J23" s="39" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="K23" s="25">
         <v>34</v>
@@ -16149,42 +16158,42 @@
         <v>11</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N23" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>236</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>238</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" s="24" t="s">
         <v>10</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J24" s="48" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K24" s="33">
         <v>35</v>
@@ -16193,18 +16202,18 @@
         <v>11</v>
       </c>
       <c r="M24" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N24" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" s="15" t="str">
         <f>VLOOKUP($E25,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16214,22 +16223,22 @@
         <v>14</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J25" s="93" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K25" s="25">
         <v>36</v>
@@ -16238,18 +16247,18 @@
         <v>11</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N25" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="24" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C26" s="31" t="str">
         <f>VLOOKUP($E26,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16259,22 +16268,22 @@
         <v>14</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J26" s="93" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="K26" s="25">
         <v>37</v>
@@ -16283,42 +16292,42 @@
         <v>11</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N26" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="24" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>39</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J27" s="93" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="K27" s="25">
         <v>38</v>
@@ -16327,19 +16336,19 @@
         <v>11</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N27" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O27" s="44"/>
     </row>
     <row r="28" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="15" t="str">
         <f>VLOOKUP($E28,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16349,22 +16358,22 @@
         <v>8</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J28" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K28" s="25">
         <v>39</v>
@@ -16373,43 +16382,43 @@
         <v>11</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N28" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29" s="15" t="str">
         <f>VLOOKUP($E29,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistics/Econometrics</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J29" s="39" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K29" s="25">
         <v>40</v>
@@ -16418,43 +16427,43 @@
         <v>11</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N29" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C30" s="31" t="str">
         <f>VLOOKUP($E30,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Computer Science</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J30" s="93" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="K30" s="25">
         <v>41</v>
@@ -16463,43 +16472,43 @@
         <v>11</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N30" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C31" s="15" t="str">
         <f>VLOOKUP($E31,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Empirical Economics</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J31" s="93" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="K31" s="25">
         <v>42</v>
@@ -16508,43 +16517,43 @@
         <v>11</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N31" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="15" t="str">
         <f>VLOOKUP($E32,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistics/Econometrics</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>39</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J32" s="93" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K32" s="25">
         <v>43</v>
@@ -16553,21 +16562,21 @@
         <v>11</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N32" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O32" s="94" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" s="15" t="str">
         <f>VLOOKUP($E33,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16577,22 +16586,22 @@
         <v>8</v>
       </c>
       <c r="E33" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J33" s="93" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K33" s="25">
         <v>44</v>
@@ -16601,18 +16610,18 @@
         <v>11</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N33" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="15" t="str">
         <f>VLOOKUP($E34,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -16622,22 +16631,22 @@
         <v>8</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>39</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="K34" s="25">
         <v>45</v>
@@ -16646,28 +16655,28 @@
         <v>11</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N34" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="35" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="18" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C35" s="13" t="str">
         <f>VLOOKUP($E35,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Public Economics</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>49</v>
@@ -16676,23 +16685,23 @@
         <v>16</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J35" s="39" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K35" s="35"/>
       <c r="L35" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N35" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O35" s="28"/>
       <c r="P35" s="28"/>
@@ -17701,7 +17710,7 @@
       <c r="AME35" s="28"/>
       <c r="AMF35" s="28"/>
     </row>
-    <row r="36" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="18" t="s">
         <v>46</v>
       </c>
@@ -17709,10 +17718,10 @@
         <v>47</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>48</v>
@@ -17724,13 +17733,13 @@
         <v>16</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J36" s="93" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="K36" s="35">
         <v>46</v>
@@ -17739,10 +17748,10 @@
         <v>11</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N36" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O36" s="28"/>
       <c r="P36" s="28"/>
@@ -18751,21 +18760,21 @@
       <c r="AME36" s="28"/>
       <c r="AMF36" s="28"/>
     </row>
-    <row r="37" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>49</v>
@@ -18774,23 +18783,23 @@
         <v>10</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J37" s="39" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="K37" s="35"/>
       <c r="L37" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N37" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O37" s="28"/>
       <c r="P37" s="28"/>
@@ -19801,19 +19810,19 @@
     </row>
     <row r="38" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>49</v>
@@ -19822,13 +19831,13 @@
         <v>10</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K38" s="35">
         <v>50</v>
@@ -19837,10 +19846,10 @@
         <v>11</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N38" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O38" s="28"/>
       <c r="P38" s="28"/>
@@ -20851,19 +20860,19 @@
     </row>
     <row r="39" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>291</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>49</v>
@@ -20872,13 +20881,13 @@
         <v>10</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J39" s="39" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="K39" s="35">
         <v>51</v>
@@ -20887,10 +20896,10 @@
         <v>11</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N39" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O39" s="28"/>
       <c r="P39" s="28"/>
@@ -21901,20 +21910,20 @@
     </row>
     <row r="40" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C40" s="13" t="str">
         <f>VLOOKUP($E40,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Professorship Macroeconomics</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>49</v>
@@ -21923,13 +21932,13 @@
         <v>10</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K40" s="35">
         <v>53</v>
@@ -21938,26 +21947,26 @@
         <v>11</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N40" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O40" s="101"/>
     </row>
-    <row r="41" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>49</v>
@@ -21966,13 +21975,13 @@
         <v>16</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J41" s="93" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K41" s="35">
         <v>55</v>
@@ -21981,18 +21990,18 @@
         <v>11</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N41" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="42" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C42" s="5" t="str">
         <f>VLOOKUP($E42,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -22002,7 +22011,7 @@
         <v>44</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>49</v>
@@ -22011,13 +22020,13 @@
         <v>16</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J42" s="93" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K42" s="36">
         <v>56</v>
@@ -22026,28 +22035,28 @@
         <v>11</v>
       </c>
       <c r="M42" s="18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N42" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="S42" s="52"/>
     </row>
     <row r="43" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>49</v>
@@ -22056,13 +22065,13 @@
         <v>10</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J43" s="39" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K43" s="35">
         <v>57</v>
@@ -22071,13 +22080,13 @@
         <v>11</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N43" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O43" s="96" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="P43" s="12"/>
       <c r="Q43" s="12"/>
@@ -23087,46 +23096,46 @@
     </row>
     <row r="44" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K44" s="35">
         <v>58</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N44" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O44" s="12"/>
       <c r="P44" s="12"/>
@@ -24137,19 +24146,19 @@
     </row>
     <row r="45" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C45" s="46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>49</v>
@@ -24158,25 +24167,25 @@
         <v>39</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I45" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J45" s="93" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K45" s="50">
         <v>59</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N45" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O45" s="12"/>
       <c r="P45" s="12"/>
@@ -25187,20 +25196,20 @@
     </row>
     <row r="46" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="18" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C46" s="13" t="str">
         <f>VLOOKUP($E46,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>49</v>
@@ -25209,25 +25218,25 @@
         <v>39</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K46" s="35">
         <v>59</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M46" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N46" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O46" s="12"/>
       <c r="P46" s="12"/>
@@ -26238,20 +26247,20 @@
     </row>
     <row r="47" spans="1:1020" s="28" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C47" s="13" t="str">
         <f>VLOOKUP($E47,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>49</v>
@@ -26260,23 +26269,23 @@
         <v>39</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I47" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J47" s="39"/>
       <c r="K47" s="35">
         <v>59</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M47" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N47" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O47" s="12"/>
       <c r="P47" s="12"/>
@@ -27287,20 +27296,20 @@
     </row>
     <row r="48" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C48" s="5" t="str">
         <f>VLOOKUP($E48,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>49</v>
@@ -27309,25 +27318,25 @@
         <v>39</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K48" s="36">
         <v>59</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M48" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N48" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O48" s="28"/>
       <c r="P48" s="28"/>
@@ -28338,20 +28347,20 @@
     </row>
     <row r="49" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>155</v>
       </c>
       <c r="C49" s="13" t="str">
         <f>VLOOKUP($E49,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>49</v>
@@ -28360,42 +28369,42 @@
         <v>39</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I49" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J49" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K49" s="35">
         <v>59</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M49" s="38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N49" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>49</v>
@@ -28404,13 +28413,13 @@
         <v>16</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K50" s="35">
         <v>60</v>
@@ -28419,10 +28428,10 @@
         <v>11</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N50" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O50" s="28"/>
       <c r="P50" s="28"/>
@@ -29433,34 +29442,34 @@
     </row>
     <row r="51" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J51" s="39" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="K51" s="35">
         <v>61</v>
@@ -29469,13 +29478,13 @@
         <v>11</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N51" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="52" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="18" t="s">
         <v>50</v>
       </c>
@@ -29487,7 +29496,7 @@
         <v>Professorship of Applied Economics</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E52" s="45" t="s">
         <v>48</v>
@@ -29499,87 +29508,89 @@
         <v>16</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I52" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J52" s="93" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="K52" s="51">
         <v>62</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M52" s="45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N52" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="53" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>299</v>
+        <v>573</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>364</v>
-      </c>
-      <c r="K53" s="35"/>
+        <v>362</v>
+      </c>
+      <c r="K53" s="35">
+        <v>13</v>
+      </c>
       <c r="L53" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N53" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O53" s="97" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="54" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="18" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>49</v>
@@ -29588,13 +29599,13 @@
         <v>10</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K54" s="35">
         <v>63</v>
@@ -29603,31 +29614,31 @@
         <v>11</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N54" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O54" s="97" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="55" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="18" t="s">
-        <v>89</v>
+        <v>480</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>54</v>
+        <v>574</v>
       </c>
       <c r="C55" s="13" t="str">
         <f>VLOOKUP($E55,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Professorship of Finance</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>49</v>
@@ -29636,44 +29647,46 @@
         <v>16</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J55" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="K55" s="35"/>
+        <v>272</v>
+      </c>
+      <c r="K55" s="35">
+        <v>68</v>
+      </c>
       <c r="L55" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N55" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O55" s="97" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="56" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>60</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>61</v>
       </c>
       <c r="C56" s="13" t="str">
         <f>VLOOKUP($E56,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Professorship of Finance</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>49</v>
@@ -29682,13 +29695,13 @@
         <v>10</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J56" s="39" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="K56" s="37">
         <v>66</v>
@@ -29697,18 +29710,18 @@
         <v>11</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N56" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="57" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="13" t="str">
         <f>VLOOKUP($E57,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -29718,7 +29731,7 @@
         <v>8</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>49</v>
@@ -29727,13 +29740,13 @@
         <v>39</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J57" s="93" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="K57" s="35">
         <v>67</v>
@@ -29742,28 +29755,28 @@
         <v>11</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N57" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="C58" s="13" t="str">
         <f>VLOOKUP($E58,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Economic Policy</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>49</v>
@@ -29772,34 +29785,34 @@
         <v>10</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J58" s="39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K58" s="35">
         <v>68</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N58" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O58" s="44"/>
     </row>
     <row r="59" spans="1:1020" s="76" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="71" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B59" s="72" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C59" s="73" t="str">
         <f>VLOOKUP($E59,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -29809,7 +29822,7 @@
         <v>8</v>
       </c>
       <c r="E59" s="72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F59" s="72" t="s">
         <v>49</v>
@@ -29818,13 +29831,13 @@
         <v>39</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I59" s="72" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J59" s="74" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K59" s="75">
         <v>69</v>
@@ -29833,28 +29846,28 @@
         <v>22</v>
       </c>
       <c r="M59" s="72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N59" s="106" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O59" s="83"/>
     </row>
     <row r="60" spans="1:1020" s="90" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="84" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B60" s="84" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D60" s="45" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="85" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F60" s="82" t="s">
         <v>49</v>
@@ -29863,25 +29876,25 @@
         <v>39</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J60" s="86" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="K60" s="87">
         <v>70</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M60" s="45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N60" s="107" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O60" s="88"/>
       <c r="P60" s="88"/>
@@ -30892,50 +30905,50 @@
     </row>
     <row r="61" spans="1:1020" s="60" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="53" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B61" s="55" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C61" s="54" t="str">
         <f>VLOOKUP($E61,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Uncertainty Quantification and Statistical Learning</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E61" s="55" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F61" s="55" t="s">
         <v>49</v>
       </c>
       <c r="G61" s="55" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I61" s="53" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J61" s="56" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K61" s="57">
         <v>71</v>
       </c>
       <c r="L61" s="55" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M61" s="55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N61" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O61" s="99" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="P61" s="58"/>
       <c r="Q61" s="58"/>
@@ -31945,49 +31958,49 @@
     </row>
     <row r="62" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>49</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J62" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K62" s="57">
         <v>71</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N62" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O62" s="100" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="P62" s="28"/>
       <c r="Q62" s="28"/>
@@ -32995,22 +33008,22 @@
       <c r="AME62" s="28"/>
       <c r="AMF62" s="28"/>
     </row>
-    <row r="63" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C63" s="13" t="str">
         <f>VLOOKUP($E63,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistical Methods for Big Data</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>49</v>
@@ -33019,70 +33032,70 @@
         <v>16</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J63" s="93" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="K63" s="57">
         <v>71</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N63" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="18" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C64" s="42" t="str">
         <f>VLOOKUP($E64,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J64" s="39" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K64" s="57">
         <v>71</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N64" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O64" s="17"/>
       <c r="P64" s="17"/>
@@ -34096,43 +34109,43 @@
         <v>12</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>49</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J65" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K65" s="57">
         <v>71</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N65" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O65" s="28"/>
       <c r="P65" s="28"/>
@@ -35143,198 +35156,198 @@
     </row>
     <row r="66" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C66" s="13" t="str">
         <f>VLOOKUP($E66,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Mathematical Statistics with Applications in Biometrics</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I66" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J66" s="39" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="K66" s="57">
         <v>71</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N66" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C67" s="13" t="str">
         <f>VLOOKUP($E67,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Business and Social Statistics</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I67" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J67" s="39" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="K67" s="57">
         <v>71</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N67" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="68" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C68" s="13" t="str">
         <f>VLOOKUP($E68,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I68" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J68" s="39" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K68" s="57">
         <v>71</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N68" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="69" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C69" s="13" t="str">
         <f>VLOOKUP($E69,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I69" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J69" s="39"/>
       <c r="K69" s="57">
         <v>71</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N69" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="70" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="18" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C70" s="13" t="str">
         <f>VLOOKUP($E70,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistical Methods for Big Data</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>49</v>
@@ -35343,72 +35356,72 @@
         <v>16</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I70" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J70" s="93" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="K70" s="57">
         <v>71</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N70" s="113" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O70" s="97" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" spans="1:1020" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="18" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>49</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I71" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J71" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K71" s="57">
         <v>71</v>
       </c>
       <c r="L71" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N71" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O71" s="28"/>
       <c r="P71" s="28"/>
@@ -36419,65 +36432,65 @@
     </row>
     <row r="72" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="18" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C72" s="13" t="str">
         <f>VLOOKUP($E72,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I72" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J72" s="39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K72" s="57">
         <v>71</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M72" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N72" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C73" s="13" t="str">
         <f>VLOOKUP($E73,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>49</v>
@@ -36486,43 +36499,43 @@
         <v>39</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I73" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J73" s="39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K73" s="57">
         <v>71</v>
       </c>
       <c r="L73" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M73" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N73" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C74" s="13" t="str">
         <f>VLOOKUP($E74,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>49</v>
@@ -36531,205 +36544,205 @@
         <v>39</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I74" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J74" s="39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K74" s="57">
         <v>71</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N74" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="75" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C75" s="13" t="str">
         <f>VLOOKUP($E75,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I75" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J75" s="39" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K75" s="57">
         <v>71</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M75" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N75" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C76" s="27" t="str">
         <f>VLOOKUP($E76,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I76" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J76" s="39" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K76" s="57">
         <v>71</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N76" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C77" s="13" t="str">
         <f>VLOOKUP($E77,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I77" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J77" s="39" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K77" s="57">
         <v>71</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N77" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="71" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B78" s="72" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C78" s="73" t="str">
         <f>VLOOKUP($E78,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E78" s="78" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F78" s="72" t="s">
         <v>49</v>
       </c>
       <c r="G78" s="71" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H78" s="71" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I78" s="71" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J78" s="74" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K78" s="57">
         <v>71</v>
       </c>
       <c r="L78" s="72" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M78" s="72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N78" s="106" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O78" s="76"/>
       <c r="P78" s="76"/>
@@ -37740,55 +37753,55 @@
     </row>
     <row r="79" spans="1:1020" s="90" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C79" s="13" t="str">
         <f>VLOOKUP($E79,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Faculty of Statistics</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F79" s="82" t="s">
         <v>49</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H79" s="92" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I79" s="92" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J79" s="86" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="K79" s="57">
         <v>71</v>
       </c>
       <c r="L79" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N79" s="107" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="80" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" s="65" t="str">
         <f>VLOOKUP($E80,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -37798,7 +37811,7 @@
         <v>8</v>
       </c>
       <c r="E80" s="61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F80" s="55" t="s">
         <v>49</v>
@@ -37807,28 +37820,28 @@
         <v>39</v>
       </c>
       <c r="H80" s="53" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I80" s="53" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J80" s="56" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K80" s="57">
         <v>72</v>
       </c>
       <c r="L80" s="55" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M80" s="55" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N80" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O80" s="60" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="P80" s="60"/>
       <c r="Q80" s="60"/>
@@ -38838,10 +38851,10 @@
     </row>
     <row r="81" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="18" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" s="13" t="str">
         <f>VLOOKUP($E81,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -38851,7 +38864,7 @@
         <v>8</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>49</v>
@@ -38860,33 +38873,33 @@
         <v>39</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I81" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J81" s="39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K81" s="35">
         <v>73</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M81" s="55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N81" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="82" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C82" s="13" t="str">
         <f>VLOOKUP($E82,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -38896,7 +38909,7 @@
         <v>8</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>49</v>
@@ -38905,33 +38918,33 @@
         <v>39</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J82" s="39" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K82" s="35">
         <v>73</v>
       </c>
       <c r="L82" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M82" s="55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N82" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="53" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" s="13" t="str">
         <f>VLOOKUP($E83,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -38941,7 +38954,7 @@
         <v>8</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>49</v>
@@ -38950,23 +38963,23 @@
         <v>39</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J83" s="56"/>
       <c r="K83" s="57">
         <v>73</v>
       </c>
       <c r="L83" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M83" s="55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N83" s="105" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O83" s="60"/>
       <c r="P83" s="60"/>
@@ -39977,35 +39990,35 @@
     </row>
     <row r="84" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C84" s="73" t="str">
         <f>VLOOKUP($E84,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Artificial Intelligence</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E84" s="72" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F84" s="72" t="s">
         <v>49</v>
       </c>
       <c r="G84" s="71" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H84" s="71" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I84" s="71" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J84" s="74" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K84" s="75">
         <v>74</v>
@@ -40014,10 +40027,10 @@
         <v>22</v>
       </c>
       <c r="M84" s="72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N84" s="106" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O84" s="76"/>
       <c r="P84" s="76"/>
@@ -41028,35 +41041,35 @@
     </row>
     <row r="85" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C85" s="79" t="str">
         <f>VLOOKUP($E85,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Artificial Intelligence</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E85" s="80" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F85" s="80" t="s">
         <v>49</v>
       </c>
       <c r="G85" s="80" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H85" s="80" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="I85" s="80" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J85" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K85" s="81">
         <v>75</v>
@@ -41065,10 +41078,10 @@
         <v>22</v>
       </c>
       <c r="M85" s="80" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N85" s="109" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O85" s="26"/>
       <c r="P85" s="26"/>
@@ -42077,47 +42090,47 @@
       <c r="AME85" s="26"/>
       <c r="AMF85" s="26"/>
     </row>
-    <row r="86" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="18" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B86" s="18"/>
       <c r="C86" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E86" s="62" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F86" s="55" t="s">
         <v>49</v>
       </c>
       <c r="G86" s="53" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H86" s="53"/>
       <c r="I86" s="53" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J86" s="63" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K86" s="77" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L86" s="55" t="s">
         <v>11</v>
       </c>
       <c r="M86" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N86" s="109" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O86" s="98" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P86" s="64"/>
       <c r="Q86" s="64"/>
@@ -43127,43 +43140,47 @@
     </row>
     <row r="87" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="B87" s="18"/>
+        <v>416</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>95</v>
+      </c>
       <c r="C87" s="79" t="str">
         <f>VLOOKUP($E87,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Statistics</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E87" s="62" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="H87" s="18"/>
+        <v>388</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>453</v>
+      </c>
       <c r="I87" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J87" s="63" t="s">
-        <v>432</v>
-      </c>
-      <c r="K87" s="77" t="s">
-        <v>406</v>
+        <v>429</v>
+      </c>
+      <c r="K87" s="77">
+        <v>73</v>
       </c>
       <c r="L87" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M87" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N87" s="109" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O87" s="64"/>
       <c r="P87" s="64"/>
@@ -44172,32 +44189,32 @@
       <c r="AME87" s="64"/>
       <c r="AMF87" s="64"/>
     </row>
-    <row r="88" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="18" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B88" s="18"/>
       <c r="C88" s="79" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E88" s="62" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H88" s="18"/>
       <c r="I88" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J88" s="93" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K88" s="77">
         <v>68</v>
@@ -44206,10 +44223,10 @@
         <v>11</v>
       </c>
       <c r="M88" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N88" s="114" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O88" s="64"/>
       <c r="P88" s="64"/>
@@ -45218,9 +45235,9 @@
       <c r="AME88" s="64"/>
       <c r="AMF88" s="64"/>
     </row>
-    <row r="89" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="18" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="79" t="str">
@@ -45231,35 +45248,35 @@
         <v>8</v>
       </c>
       <c r="E89" s="62" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H89" s="18"/>
       <c r="I89" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J89" s="63" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="K89" s="77" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L89" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M89" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N89" s="109" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O89" s="98" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P89" s="64"/>
       <c r="Q89" s="64"/>
@@ -46267,9 +46284,9 @@
       <c r="AME89" s="64"/>
       <c r="AMF89" s="64"/>
     </row>
-    <row r="90" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="62" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="79" t="str">
@@ -46280,35 +46297,35 @@
         <v>8</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H90" s="18"/>
       <c r="I90" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J90" s="63" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K90" s="77" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L90" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M90" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N90" s="109" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O90" s="98" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P90" s="64"/>
       <c r="Q90" s="64"/>
@@ -47318,7 +47335,7 @@
     </row>
     <row r="91" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="62" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B91" s="18"/>
       <c r="C91" s="79" t="str">
@@ -47329,37 +47346,37 @@
         <v>8</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I91" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J91" s="93" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K91" s="77" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L91" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M91" s="62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N91" s="114" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O91" s="98" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P91" s="64"/>
       <c r="Q91" s="64"/>
@@ -48367,9 +48384,9 @@
       <c r="AME91" s="64"/>
       <c r="AMF91" s="64"/>
     </row>
-    <row r="92" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:1020" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="62" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="79" t="str">
@@ -48380,35 +48397,35 @@
         <v>8</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H92" s="18"/>
       <c r="I92" s="18" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J92" s="63" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="K92" s="77" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="L92" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M92" s="62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N92" s="109" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O92" s="98" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P92" s="64"/>
       <c r="Q92" s="64"/>
@@ -49432,7 +49449,7 @@
         <v>8</v>
       </c>
       <c r="E93" s="68" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F93" s="68" t="s">
         <v>9</v>
@@ -49441,13 +49458,13 @@
         <v>10</v>
       </c>
       <c r="H93" s="68" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I93" s="68" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J93" s="56" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K93" s="70">
         <v>76</v>
@@ -49456,10 +49473,10 @@
         <v>11</v>
       </c>
       <c r="M93" s="68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N93" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O93" s="60"/>
       <c r="P93" s="60"/>
@@ -50470,19 +50487,19 @@
     </row>
     <row r="94" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="B94" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>304</v>
-      </c>
       <c r="D94" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F94" s="10" t="s">
         <v>9</v>
@@ -50491,13 +50508,13 @@
         <v>16</v>
       </c>
       <c r="H94" s="68" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I94" s="68" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J94" s="39" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="K94" s="34">
         <v>77</v>
@@ -50506,27 +50523,27 @@
         <v>11</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N94" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="95" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="19" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>9</v>
@@ -50535,13 +50552,13 @@
         <v>10</v>
       </c>
       <c r="H95" s="68" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I95" s="68" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J95" s="39" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K95" s="34">
         <v>78</v>
@@ -50550,24 +50567,24 @@
         <v>11</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N95" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="96" spans="1:1020" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="19" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>31</v>
@@ -50579,13 +50596,13 @@
         <v>16</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J96" s="39" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K96" s="34">
         <v>79</v>
@@ -50594,27 +50611,27 @@
         <v>11</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N96" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C97" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B97" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>245</v>
-      </c>
       <c r="D97" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>9</v>
@@ -50623,13 +50640,13 @@
         <v>16</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J97" s="93" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="K97" s="34">
         <v>80</v>
@@ -50638,10 +50655,10 @@
         <v>11</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N97" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -50656,7 +50673,7 @@
         <v>Chair of Microeconomics</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>20</v>
@@ -50668,13 +50685,13 @@
         <v>10</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I98" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J98" s="39" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K98" s="22">
         <v>81</v>
@@ -50683,25 +50700,25 @@
         <v>22</v>
       </c>
       <c r="M98" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N98" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C99" s="14" t="str">
         <f>VLOOKUP($E99,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of International Economics</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>31</v>
@@ -50713,13 +50730,13 @@
         <v>10</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I99" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J99" s="93" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="K99" s="22">
         <v>82</v>
@@ -50728,18 +50745,18 @@
         <v>11</v>
       </c>
       <c r="M99" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N99" s="112" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C100" s="14" t="str">
         <f>VLOOKUP($E100,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -50749,7 +50766,7 @@
         <v>14</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F100" s="10" t="s">
         <v>9</v>
@@ -50758,13 +50775,13 @@
         <v>10</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I100" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J100" s="39" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K100" s="22">
         <v>83</v>
@@ -50773,18 +50790,18 @@
         <v>11</v>
       </c>
       <c r="M100" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N100" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C101" s="6" t="str">
         <f>VLOOKUP($E101,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -50794,7 +50811,7 @@
         <v>14</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F101" s="19" t="s">
         <v>9</v>
@@ -50803,13 +50820,13 @@
         <v>16</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I101" s="19" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J101" s="93" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="K101" s="32">
         <v>84</v>
@@ -50818,10 +50835,10 @@
         <v>11</v>
       </c>
       <c r="M101" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N101" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="102" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -50848,13 +50865,13 @@
         <v>39</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I102" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J102" s="39" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="K102" s="22">
         <v>85</v>
@@ -50863,18 +50880,18 @@
         <v>34</v>
       </c>
       <c r="M102" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N102" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C103" s="14" t="str">
         <f>VLOOKUP($E103,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -50893,13 +50910,13 @@
         <v>10</v>
       </c>
       <c r="H103" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I103" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J103" s="39" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K103" s="34">
         <v>86</v>
@@ -50908,18 +50925,18 @@
         <v>11</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N103" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C104" s="6" t="str">
         <f>VLOOKUP($E104,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -50929,7 +50946,7 @@
         <v>8</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F104" s="19" t="s">
         <v>9</v>
@@ -50938,13 +50955,13 @@
         <v>16</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I104" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J104" s="93" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K104" s="32">
         <v>87</v>
@@ -50953,18 +50970,18 @@
         <v>11</v>
       </c>
       <c r="M104" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N104" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="105" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C105" s="6" t="str">
         <f>VLOOKUP($E105,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -50974,7 +50991,7 @@
         <v>8</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F105" s="19" t="s">
         <v>9</v>
@@ -50983,13 +51000,13 @@
         <v>10</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I105" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J105" s="39" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K105" s="32">
         <v>88</v>
@@ -50998,18 +51015,18 @@
         <v>34</v>
       </c>
       <c r="M105" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N105" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C106" s="14" t="str">
         <f>VLOOKUP($E106,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -51019,7 +51036,7 @@
         <v>8</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F106" s="10" t="s">
         <v>9</v>
@@ -51028,13 +51045,13 @@
         <v>10</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I106" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J106" s="39" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K106" s="22">
         <v>89</v>
@@ -51043,13 +51060,13 @@
         <v>22</v>
       </c>
       <c r="M106" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N106" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="19" t="s">
         <v>43</v>
       </c>
@@ -51073,13 +51090,13 @@
         <v>16</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I107" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J107" s="93" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="K107" s="22">
         <v>90</v>
@@ -51088,25 +51105,25 @@
         <v>11</v>
       </c>
       <c r="M107" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N107" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C108" s="14" t="str">
         <f>VLOOKUP($E108,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Econometrics</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>15</v>
@@ -51118,13 +51135,13 @@
         <v>10</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J108" s="93" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K108" s="34">
         <v>91</v>
@@ -51133,18 +51150,18 @@
         <v>11</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N108" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C109" s="14" t="str">
         <f>VLOOKUP($E109,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -51154,7 +51171,7 @@
         <v>14</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>9</v>
@@ -51163,13 +51180,13 @@
         <v>10</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J109" s="39" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K109" s="34">
         <v>93</v>
@@ -51178,10 +51195,10 @@
         <v>11</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N109" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51197,10 +51214,10 @@
  esp. Economics of Renewable Energy</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F110" s="10" t="s">
         <v>9</v>
@@ -51209,13 +51226,13 @@
         <v>16</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I110" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J110" s="39" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K110" s="22">
         <v>94</v>
@@ -51224,13 +51241,13 @@
         <v>11</v>
       </c>
       <c r="M110" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N110" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="19" t="s">
         <v>24</v>
       </c>
@@ -51242,7 +51259,7 @@
         <v>Chair of Statistics</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>25</v>
@@ -51254,13 +51271,13 @@
         <v>16</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J111" s="93" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="K111" s="22">
         <v>95</v>
@@ -51269,18 +51286,18 @@
         <v>22</v>
       </c>
       <c r="M111" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N111" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C112" s="14" t="str">
         <f>VLOOKUP($E112,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -51290,34 +51307,34 @@
         <v>14</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G112" s="20" t="s">
         <v>10</v>
       </c>
       <c r="H112" s="19" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I112" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J112" s="39" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K112" s="22">
         <v>96</v>
       </c>
       <c r="L112" s="21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M112" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N112" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="113" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51332,7 +51349,7 @@
         <v>Chair of Statistics</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>25</v>
@@ -51344,13 +51361,13 @@
         <v>10</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I113" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J113" s="39" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="K113" s="22">
         <v>97</v>
@@ -51359,10 +51376,10 @@
         <v>22</v>
       </c>
       <c r="M113" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N113" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="114" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51377,7 +51394,7 @@
         <v>Chair for Energy Trading and Finance</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>28</v>
@@ -51389,13 +51406,13 @@
         <v>10</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I114" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J114" s="39" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K114" s="22">
         <v>98</v>
@@ -51404,10 +51421,10 @@
         <v>11</v>
       </c>
       <c r="M114" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N114" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="115" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51422,7 +51439,7 @@
         <v>Chair for Energy Trading and Finance</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>28</v>
@@ -51434,13 +51451,13 @@
         <v>10</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I115" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J115" s="39" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K115" s="22">
         <v>99</v>
@@ -51449,10 +51466,10 @@
         <v>11</v>
       </c>
       <c r="M115" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N115" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="116" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51467,7 +51484,7 @@
         <v>Chair of Health Economics</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>18</v>
@@ -51479,13 +51496,13 @@
         <v>10</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I116" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J116" s="39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K116" s="22">
         <v>100</v>
@@ -51494,28 +51511,28 @@
         <v>11</v>
       </c>
       <c r="M116" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N116" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C117" s="14" t="str">
         <f>VLOOKUP($E117,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Labour and Health Economics</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>9</v>
@@ -51524,13 +51541,13 @@
         <v>16</v>
       </c>
       <c r="H117" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I117" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J117" s="39" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="K117" s="22">
         <v>101</v>
@@ -51539,13 +51556,13 @@
         <v>11</v>
       </c>
       <c r="M117" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N117" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="19" t="s">
         <v>33</v>
       </c>
@@ -51558,10 +51575,10 @@
  esp. Economics of Renewable Energy</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F118" s="10" t="s">
         <v>9</v>
@@ -51570,13 +51587,13 @@
         <v>16</v>
       </c>
       <c r="H118" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J118" s="93" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="K118" s="22">
         <v>102</v>
@@ -51585,18 +51602,18 @@
         <v>11</v>
       </c>
       <c r="M118" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N118" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C119" s="14" t="str">
         <f>VLOOKUP($E119,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -51615,13 +51632,13 @@
         <v>39</v>
       </c>
       <c r="H119" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I119" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J119" s="93" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="K119" s="22">
         <v>103</v>
@@ -51630,10 +51647,10 @@
         <v>11</v>
       </c>
       <c r="M119" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N119" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="120" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51648,7 +51665,7 @@
         <v>Chair of International Economics</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>31</v>
@@ -51660,13 +51677,13 @@
         <v>10</v>
       </c>
       <c r="H120" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J120" s="39" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K120" s="22">
         <v>105</v>
@@ -51675,13 +51692,13 @@
         <v>22</v>
       </c>
       <c r="M120" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N120" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="19" t="s">
         <v>36</v>
       </c>
@@ -51693,7 +51710,7 @@
         <v>Chair for Energy Trading and Finance</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>28</v>
@@ -51705,13 +51722,13 @@
         <v>16</v>
       </c>
       <c r="H121" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I121" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J121" s="93" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="K121" s="22">
         <v>106</v>
@@ -51720,18 +51737,18 @@
         <v>11</v>
       </c>
       <c r="M121" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N121" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="19" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C122" s="14" t="str">
         <f>VLOOKUP($E122,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -51750,13 +51767,13 @@
         <v>16</v>
       </c>
       <c r="H122" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I122" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J122" s="93" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="K122" s="22">
         <v>107</v>
@@ -51765,10 +51782,10 @@
         <v>11</v>
       </c>
       <c r="M122" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N122" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51783,7 +51800,7 @@
         <v>Chair of Econometrics</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>15</v>
@@ -51792,16 +51809,16 @@
         <v>9</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I123" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J123" s="39" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="K123" s="22">
         <v>108</v>
@@ -51810,10 +51827,10 @@
         <v>11</v>
       </c>
       <c r="M123" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N123" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="124" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51828,7 +51845,7 @@
         <v>Chair of Health Economics</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>18</v>
@@ -51840,13 +51857,13 @@
         <v>16</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I124" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J124" s="93" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="K124" s="22">
         <v>109</v>
@@ -51855,25 +51872,25 @@
         <v>11</v>
       </c>
       <c r="M124" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N124" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="125" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="19" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C125" s="14" t="str">
         <f>VLOOKUP($E125,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Econometrics</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>15</v>
@@ -51882,28 +51899,28 @@
         <v>9</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I125" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J125" s="39" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="K125" s="22">
         <v>110</v>
       </c>
       <c r="L125" s="21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M125" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N125" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -51918,7 +51935,7 @@
         <v>Chair of Econometrics</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>15</v>
@@ -51927,13 +51944,13 @@
         <v>9</v>
       </c>
       <c r="G126" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I126" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J126" s="39"/>
       <c r="K126" s="22">
@@ -51943,62 +51960,62 @@
         <v>11</v>
       </c>
       <c r="M126" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N126" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J127" s="93" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="K127" s="22">
         <v>112</v>
       </c>
       <c r="L127" s="21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M127" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N127" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:14" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="19" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C128" s="14" t="str">
         <f>VLOOKUP($E128,Liste!$A$2:$C$59,2,FALSE)</f>
@@ -52014,33 +52031,33 @@
         <v>9</v>
       </c>
       <c r="G128" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J128" s="93" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="K128" s="22">
         <v>113</v>
       </c>
       <c r="L128" s="21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M128" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N128" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:15" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>41</v>
@@ -52050,7 +52067,7 @@
         <v>Chair of Econometrics</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>15</v>
@@ -52059,16 +52076,16 @@
         <v>9</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I129" s="20" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J129" s="93" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="K129" s="22">
         <v>114</v>
@@ -52077,15 +52094,15 @@
         <v>11</v>
       </c>
       <c r="M129" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N129" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:15" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>13</v>
@@ -52095,7 +52112,7 @@
         <v>Chair of Econometrics</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E130" s="10" t="s">
         <v>15</v>
@@ -52104,16 +52121,16 @@
         <v>9</v>
       </c>
       <c r="G130" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H130" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J130" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K130" s="22">
         <v>115</v>
@@ -52122,13 +52139,13 @@
         <v>11</v>
       </c>
       <c r="M130" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N130" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:15" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="19" t="s">
         <v>42</v>
       </c>
@@ -52152,13 +52169,13 @@
         <v>16</v>
       </c>
       <c r="H131" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I131" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J131" s="93" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="K131" s="22">
         <v>116</v>
@@ -52167,10 +52184,10 @@
         <v>22</v>
       </c>
       <c r="M131" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N131" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:15" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -52185,7 +52202,7 @@
         <v>Chair of Statistics</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>25</v>
@@ -52197,13 +52214,13 @@
         <v>16</v>
       </c>
       <c r="H132" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J132" s="39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K132" s="22">
         <v>117</v>
@@ -52212,25 +52229,25 @@
         <v>22</v>
       </c>
       <c r="M132" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N132" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:15" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C133" s="14" t="str">
         <f>VLOOKUP($E133,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair of Econometrics</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>15</v>
@@ -52239,16 +52256,16 @@
         <v>9</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H133" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I133" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J133" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K133" s="22">
         <v>118</v>
@@ -52257,25 +52274,25 @@
         <v>34</v>
       </c>
       <c r="M133" s="23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N133" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:15" ht="47.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="19" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C134" s="14" t="str">
         <f>VLOOKUP($E134,Liste!$A$2:$C$59,2,FALSE)</f>
         <v>Chair for Energy Trading and Finance</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E134" s="10" t="s">
         <v>28</v>
@@ -52284,16 +52301,16 @@
         <v>9</v>
       </c>
       <c r="G134" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H134" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I134" s="20" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J134" s="39" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="K134" s="22">
         <v>92</v>
@@ -52302,90 +52319,102 @@
         <v>11</v>
       </c>
       <c r="M134" s="23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" ht="47.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="C135" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="10" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="B135" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="C135" s="14"/>
-      <c r="D135" s="10"/>
-      <c r="E135" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H135" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I135" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J135" s="93" t="s">
-        <v>556</v>
-      </c>
-      <c r="K135" s="22"/>
+        <v>553</v>
+      </c>
+      <c r="K135" s="22">
+        <v>79</v>
+      </c>
       <c r="L135" s="21" t="s">
         <v>11</v>
       </c>
       <c r="M135" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N135" s="111"/>
     </row>
-    <row r="136" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15" ht="47.45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="19" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="C136" s="14"/>
-      <c r="D136" s="10"/>
+        <v>484</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="E136" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F136" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G136" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H136" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I136" s="20" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J136" s="93" t="s">
-        <v>557</v>
-      </c>
-      <c r="K136" s="22"/>
+        <v>554</v>
+      </c>
+      <c r="K136" s="22">
+        <v>99</v>
+      </c>
       <c r="L136" s="21" t="s">
         <v>11</v>
       </c>
       <c r="M136" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N136" s="111"/>
     </row>
     <row r="137" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="19" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B137" s="19"/>
       <c r="C137" s="14"/>
       <c r="D137" s="10"/>
       <c r="E137" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>9</v>
@@ -52394,10 +52423,10 @@
         <v>16</v>
       </c>
       <c r="H137" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I137" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J137" s="39"/>
       <c r="K137" s="22"/>
@@ -52405,21 +52434,25 @@
         <v>11</v>
       </c>
       <c r="M137" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N137" s="111"/>
       <c r="O137" s="12" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:15" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="B138" s="10"/>
-      <c r="C138" s="10"/>
+        <v>519</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>575</v>
+      </c>
       <c r="D138" s="10" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E138" s="10" t="s">
         <v>18</v>
@@ -52428,51 +52461,55 @@
         <v>9</v>
       </c>
       <c r="G138" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H138" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="I138" s="20"/>
+        <v>454</v>
+      </c>
+      <c r="I138" s="20" t="s">
+        <v>398</v>
+      </c>
       <c r="J138" s="93" t="s">
-        <v>557</v>
-      </c>
-      <c r="K138" s="22"/>
+        <v>554</v>
+      </c>
+      <c r="K138" s="22">
+        <v>91</v>
+      </c>
       <c r="L138" s="21" t="s">
         <v>11</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N138" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="139" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="19" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B139" s="19" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C139" s="14"/>
       <c r="D139" s="10" t="s">
         <v>8</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H139" s="19" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I139" s="20" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J139" s="39"/>
       <c r="K139" s="22"/>
@@ -52480,48 +52517,56 @@
         <v>11</v>
       </c>
       <c r="M139" s="23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N139" s="111"/>
       <c r="O139" s="12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15" s="12" customFormat="1" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="24" t="s">
-        <v>493</v>
-      </c>
-      <c r="B140" s="11"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="C140" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>445</v>
+      </c>
       <c r="E140" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G140" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J140" s="93" t="s">
-        <v>558</v>
-      </c>
-      <c r="K140" s="25"/>
+        <v>555</v>
+      </c>
+      <c r="K140" s="25">
+        <v>27</v>
+      </c>
       <c r="L140" s="11" t="s">
         <v>11</v>
       </c>
       <c r="M140" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N140" s="111"/>
     </row>
-    <row r="141" spans="1:15" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:15" ht="65.099999999999994" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="18" t="s">
         <v>52</v>
       </c>
@@ -52533,7 +52578,7 @@
         <v>Professorship of Applied Economics</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>48</v>
@@ -52545,33 +52590,33 @@
         <v>10</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I141" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J141" s="93" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="K141" s="57" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="L141" s="9" t="s">
         <v>22</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N141" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O141" s="97" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="142" spans="1:15" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="18" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>53</v>
@@ -52592,32 +52637,34 @@
       <c r="G142" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H142" s="9"/>
+      <c r="H142" s="9" t="s">
+        <v>449</v>
+      </c>
       <c r="I142" s="9" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="J142" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="K142" s="57" t="s">
-        <v>387</v>
+        <v>442</v>
+      </c>
+      <c r="K142" s="57">
+        <v>48</v>
       </c>
       <c r="L142" s="9" t="s">
         <v>34</v>
       </c>
       <c r="M142" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N142" s="108" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O142" s="97" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:15" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="18" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B143" s="9"/>
       <c r="C143" s="13" t="str">
@@ -52625,10 +52672,10 @@
         <v>Professorship of Finance</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>49</v>
@@ -52637,13 +52684,13 @@
         <v>39</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I143" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J143" s="93" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="K143" s="57">
         <v>65</v>
@@ -52652,23 +52699,27 @@
         <v>11</v>
       </c>
       <c r="M143" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N143" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:15" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="18" t="s">
-        <v>495</v>
-      </c>
-      <c r="B144" s="9"/>
-      <c r="C144" s="13"/>
+        <v>492</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C144" s="13" t="s">
+        <v>295</v>
+      </c>
       <c r="D144" s="9" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>49</v>
@@ -52677,140 +52728,150 @@
         <v>39</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I144" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J144" s="93" t="s">
-        <v>561</v>
-      </c>
-      <c r="K144" s="57"/>
+        <v>558</v>
+      </c>
+      <c r="K144" s="57">
+        <v>51</v>
+      </c>
       <c r="L144" s="55" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M144" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N144" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="18" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B145" s="9"/>
       <c r="C145" s="13"/>
       <c r="D145" s="9"/>
       <c r="E145" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I145" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J145" s="93" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="K145" s="57"/>
       <c r="L145" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N145" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:14" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="18" t="s">
-        <v>501</v>
-      </c>
-      <c r="B146" s="9"/>
+        <v>498</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>498</v>
+      </c>
       <c r="C146" s="13"/>
       <c r="D146" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I146" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J146" s="93" t="s">
-        <v>563</v>
-      </c>
-      <c r="K146" s="57"/>
+        <v>560</v>
+      </c>
+      <c r="K146" s="57">
+        <v>15</v>
+      </c>
       <c r="L146" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N146" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:14" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="18" t="s">
-        <v>504</v>
-      </c>
-      <c r="B147" s="9"/>
+        <v>501</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>501</v>
+      </c>
       <c r="C147" s="13"/>
       <c r="D147" s="9" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I147" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J147" s="93" t="s">
-        <v>564</v>
-      </c>
-      <c r="K147" s="57"/>
+        <v>561</v>
+      </c>
+      <c r="K147" s="57">
+        <v>15</v>
+      </c>
       <c r="L147" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N147" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="18" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B148" s="9"/>
       <c r="C148" s="13"/>
@@ -52818,37 +52879,37 @@
         <v>8</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I148" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J148" s="93" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="K148" s="57"/>
       <c r="L148" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M148" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N148" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="18" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B149" s="9"/>
       <c r="C149" s="13"/>
@@ -52856,37 +52917,37 @@
         <v>8</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I149" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J149" s="93" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K149" s="57"/>
       <c r="L149" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N149" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="18" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B150" s="9"/>
       <c r="C150" s="13"/>
@@ -52894,37 +52955,37 @@
         <v>8</v>
       </c>
       <c r="E150" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H150" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I150" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J150" s="93" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="K150" s="57"/>
       <c r="L150" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M150" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N150" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="18" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B151" s="9"/>
       <c r="C151" s="13"/>
@@ -52932,37 +52993,37 @@
         <v>8</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I151" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J151" s="93" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K151" s="57"/>
       <c r="L151" s="9" t="s">
         <v>22</v>
       </c>
       <c r="M151" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N151" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="152" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="18" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B152" s="9"/>
       <c r="C152" s="13"/>
@@ -52970,37 +53031,37 @@
         <v>8</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H152" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I152" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J152" s="93" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="K152" s="57"/>
       <c r="L152" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N152" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="18" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B153" s="9"/>
       <c r="C153" s="13"/>
@@ -53008,37 +53069,37 @@
         <v>8</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I153" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J153" s="93" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="K153" s="57"/>
       <c r="L153" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N153" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="154" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="18" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B154" s="9"/>
       <c r="C154" s="13"/>
@@ -53046,116 +53107,116 @@
         <v>8</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H154" s="9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I154" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J154" s="93" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="K154" s="57"/>
       <c r="L154" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M154" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N154" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="18" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B155" s="9"/>
       <c r="C155" s="13"/>
       <c r="D155" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I155" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J155" s="93" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="K155" s="57"/>
       <c r="L155" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N155" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" spans="1:14" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="18" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B156" s="9"/>
       <c r="C156" s="13"/>
       <c r="D156" s="9" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>49</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J156" s="93" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="K156" s="57"/>
       <c r="L156" s="9" t="s">
         <v>22</v>
       </c>
       <c r="M156" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N156" s="102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="A1:AMF156" xr:uid="{74FC7BA3-A876-4AC0-9905-EF4CDF2546B3}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="yes"/>
+    <filterColumn colId="10">
+      <filters blank="1">
+        <filter val="NA"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AMF133">
